--- a/AAII_Financials/Quarterly/FFWC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FFWC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>FFWC</t>
   </si>
@@ -656,174 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42916</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42825</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42643</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>41547</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4500</v>
-      </c>
-      <c r="I8" s="3">
-        <v>4100</v>
       </c>
       <c r="J8" s="3">
         <v>4100</v>
       </c>
       <c r="K8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="L8" s="3">
         <v>4200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4100</v>
-      </c>
-      <c r="N8" s="3">
-        <v>4300</v>
       </c>
       <c r="O8" s="3">
         <v>4300</v>
@@ -832,43 +836,43 @@
         <v>4300</v>
       </c>
       <c r="Q8" s="3">
+        <v>4300</v>
+      </c>
+      <c r="R8" s="3">
         <v>4500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4100</v>
-      </c>
-      <c r="W8" s="3">
-        <v>4000</v>
       </c>
       <c r="X8" s="3">
         <v>4000</v>
       </c>
       <c r="Y8" s="3">
-        <v>3700</v>
+        <v>4000</v>
       </c>
       <c r="Z8" s="3">
         <v>3700</v>
       </c>
       <c r="AA8" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AB8" s="3">
         <v>3800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3500</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>3300</v>
       </c>
       <c r="AD8" s="3">
         <v>3300</v>
@@ -879,8 +883,11 @@
       <c r="AF8" s="3">
         <v>3300</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -971,8 +978,11 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1063,8 +1073,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1097,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1189,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1281,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1373,8 +1393,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1465,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1496,28 +1522,29 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E17" s="3">
         <v>2200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>600</v>
-      </c>
-      <c r="I17" s="3">
-        <v>400</v>
       </c>
       <c r="J17" s="3">
         <v>400</v>
@@ -1526,55 +1553,55 @@
         <v>400</v>
       </c>
       <c r="L17" s="3">
+        <v>400</v>
+      </c>
+      <c r="M17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>700</v>
-      </c>
-      <c r="O17" s="3">
-        <v>800</v>
       </c>
       <c r="P17" s="3">
         <v>800</v>
       </c>
       <c r="Q17" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="R17" s="3">
         <v>1000</v>
       </c>
       <c r="S17" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="T17" s="3">
         <v>1100</v>
       </c>
       <c r="U17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V17" s="3">
         <v>1000</v>
-      </c>
-      <c r="V17" s="3">
-        <v>800</v>
       </c>
       <c r="W17" s="3">
         <v>800</v>
       </c>
       <c r="X17" s="3">
+        <v>800</v>
+      </c>
+      <c r="Y17" s="3">
         <v>500</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>600</v>
       </c>
       <c r="Z17" s="3">
         <v>600</v>
       </c>
       <c r="AA17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB17" s="3">
         <v>100</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>500</v>
       </c>
       <c r="AC17" s="3">
         <v>500</v>
@@ -1583,51 +1610,54 @@
         <v>500</v>
       </c>
       <c r="AE17" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF17" s="3">
         <v>600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E18" s="3">
         <v>3700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3900</v>
-      </c>
-      <c r="I18" s="3">
-        <v>3700</v>
       </c>
       <c r="J18" s="3">
         <v>3700</v>
       </c>
       <c r="K18" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="L18" s="3">
         <v>3800</v>
       </c>
       <c r="M18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="N18" s="3">
         <v>3500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3600</v>
-      </c>
-      <c r="O18" s="3">
-        <v>3500</v>
       </c>
       <c r="P18" s="3">
         <v>3500</v>
@@ -1636,52 +1666,55 @@
         <v>3500</v>
       </c>
       <c r="R18" s="3">
+        <v>3500</v>
+      </c>
+      <c r="S18" s="3">
         <v>3300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3400</v>
-      </c>
-      <c r="T18" s="3">
-        <v>3200</v>
       </c>
       <c r="U18" s="3">
         <v>3200</v>
       </c>
       <c r="V18" s="3">
+        <v>3200</v>
+      </c>
+      <c r="W18" s="3">
         <v>3300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3500</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>3100</v>
       </c>
       <c r="Z18" s="3">
         <v>3100</v>
       </c>
       <c r="AA18" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AB18" s="3">
         <v>3700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3000</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>2800</v>
       </c>
       <c r="AD18" s="3">
         <v>2800</v>
       </c>
       <c r="AE18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AF18" s="3">
         <v>2700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1714,25 +1747,26 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-2200</v>
       </c>
       <c r="I20" s="3">
         <v>-2200</v>
@@ -1741,31 +1775,31 @@
         <v>-2200</v>
       </c>
       <c r="K20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-1400</v>
       </c>
       <c r="O20" s="3">
         <v>-1400</v>
       </c>
       <c r="P20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-2000</v>
       </c>
       <c r="T20" s="3">
         <v>-2000</v>
@@ -1777,13 +1811,13 @@
         <v>-2000</v>
       </c>
       <c r="W20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="X20" s="3">
         <v>-1900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2100</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-1800</v>
       </c>
       <c r="Z20" s="3">
         <v>-1800</v>
@@ -1792,22 +1826,25 @@
         <v>-1800</v>
       </c>
       <c r="AB20" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="AC20" s="3">
         <v>-1700</v>
       </c>
       <c r="AD20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1898,8 +1935,11 @@
       <c r="AF21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1990,73 +2030,76 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E23" s="3">
         <v>1400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1700</v>
-      </c>
-      <c r="I23" s="3">
-        <v>1500</v>
       </c>
       <c r="J23" s="3">
         <v>1500</v>
       </c>
       <c r="K23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L23" s="3">
         <v>1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1800</v>
-      </c>
-      <c r="N23" s="3">
-        <v>2100</v>
       </c>
       <c r="O23" s="3">
         <v>2100</v>
       </c>
       <c r="P23" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Q23" s="3">
         <v>1700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1400</v>
-      </c>
-      <c r="T23" s="3">
-        <v>1200</v>
       </c>
       <c r="U23" s="3">
         <v>1200</v>
       </c>
       <c r="V23" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="W23" s="3">
         <v>1300</v>
       </c>
       <c r="X23" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="Y23" s="3">
         <v>1400</v>
@@ -2065,25 +2108,28 @@
         <v>1400</v>
       </c>
       <c r="AA23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AB23" s="3">
         <v>1900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1100</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>1300</v>
       </c>
       <c r="AE23" s="3">
         <v>1300</v>
       </c>
       <c r="AF23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AG23" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2094,28 +2140,28 @@
         <v>100</v>
       </c>
       <c r="F24" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>300</v>
       </c>
       <c r="H24" s="3">
+        <v>300</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
-      </c>
-      <c r="M24" s="3">
-        <v>300</v>
       </c>
       <c r="N24" s="3">
         <v>300</v>
@@ -2127,7 +2173,7 @@
         <v>300</v>
       </c>
       <c r="Q24" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R24" s="3">
         <v>200</v>
@@ -2136,16 +2182,16 @@
         <v>200</v>
       </c>
       <c r="T24" s="3">
+        <v>200</v>
+      </c>
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>100</v>
-      </c>
-      <c r="W24" s="3">
-        <v>200</v>
       </c>
       <c r="X24" s="3">
         <v>200</v>
@@ -2157,25 +2203,28 @@
         <v>200</v>
       </c>
       <c r="AA24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB24" s="3">
         <v>500</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>200</v>
       </c>
       <c r="AC24" s="3">
         <v>200</v>
       </c>
       <c r="AD24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AE24" s="3">
         <v>300</v>
       </c>
       <c r="AF24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2266,64 +2315,67 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1500</v>
-      </c>
-      <c r="I26" s="3">
-        <v>1400</v>
       </c>
       <c r="J26" s="3">
         <v>1400</v>
       </c>
       <c r="K26" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L26" s="3">
         <v>1500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1000</v>
-      </c>
-      <c r="U26" s="3">
-        <v>1100</v>
       </c>
       <c r="V26" s="3">
         <v>1100</v>
@@ -2341,81 +2393,84 @@
         <v>1100</v>
       </c>
       <c r="AA26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB26" s="3">
         <v>1400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>900</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>1000</v>
       </c>
       <c r="AE26" s="3">
         <v>1000</v>
       </c>
       <c r="AF26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1500</v>
-      </c>
-      <c r="I27" s="3">
-        <v>1400</v>
       </c>
       <c r="J27" s="3">
         <v>1400</v>
       </c>
       <c r="K27" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L27" s="3">
         <v>1500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1000</v>
-      </c>
-      <c r="U27" s="3">
-        <v>1100</v>
       </c>
       <c r="V27" s="3">
         <v>1100</v>
@@ -2433,25 +2488,28 @@
         <v>1100</v>
       </c>
       <c r="AA27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB27" s="3">
         <v>1400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>900</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>1000</v>
       </c>
       <c r="AE27" s="3">
         <v>1000</v>
       </c>
       <c r="AF27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2542,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2634,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2726,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2818,25 +2885,28 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E32" s="3">
         <v>2300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2200</v>
       </c>
       <c r="I32" s="3">
         <v>2200</v>
@@ -2845,31 +2915,31 @@
         <v>2200</v>
       </c>
       <c r="K32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1600</v>
-      </c>
-      <c r="N32" s="3">
-        <v>1400</v>
       </c>
       <c r="O32" s="3">
         <v>1400</v>
       </c>
       <c r="P32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q32" s="3">
         <v>1900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1800</v>
-      </c>
-      <c r="S32" s="3">
-        <v>2000</v>
       </c>
       <c r="T32" s="3">
         <v>2000</v>
@@ -2881,13 +2951,13 @@
         <v>2000</v>
       </c>
       <c r="W32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X32" s="3">
         <v>1900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2100</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>1800</v>
       </c>
       <c r="Z32" s="3">
         <v>1800</v>
@@ -2896,78 +2966,81 @@
         <v>1800</v>
       </c>
       <c r="AB32" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="AC32" s="3">
         <v>1700</v>
       </c>
       <c r="AD32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AE32" s="3">
         <v>1500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1500</v>
-      </c>
-      <c r="I33" s="3">
-        <v>1400</v>
       </c>
       <c r="J33" s="3">
         <v>1400</v>
       </c>
       <c r="K33" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L33" s="3">
         <v>1500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1000</v>
-      </c>
-      <c r="U33" s="3">
-        <v>1100</v>
       </c>
       <c r="V33" s="3">
         <v>1100</v>
@@ -2985,25 +3058,28 @@
         <v>1100</v>
       </c>
       <c r="AA33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB33" s="3">
         <v>1400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>900</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>1000</v>
       </c>
       <c r="AE33" s="3">
         <v>1000</v>
       </c>
       <c r="AF33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3094,64 +3170,67 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1500</v>
-      </c>
-      <c r="I35" s="3">
-        <v>1400</v>
       </c>
       <c r="J35" s="3">
         <v>1400</v>
       </c>
       <c r="K35" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L35" s="3">
         <v>1500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1000</v>
-      </c>
-      <c r="U35" s="3">
-        <v>1100</v>
       </c>
       <c r="V35" s="3">
         <v>1100</v>
@@ -3169,122 +3248,128 @@
         <v>1100</v>
       </c>
       <c r="AA35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB35" s="3">
         <v>1400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>900</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>1000</v>
       </c>
       <c r="AE35" s="3">
         <v>1000</v>
       </c>
       <c r="AF35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42916</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42825</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42643</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>41547</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3317,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3351,192 +3437,199 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E41" s="3">
         <v>8700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E42" s="3">
         <v>6000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>14200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>49700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>63100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>66000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>49500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>53100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>43400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>23600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>28400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>31500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>14000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>16500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>13100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>23300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>21100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>24900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>17900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>13200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>9000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>16600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>19700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>16900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>17300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>15500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>7100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3627,8 +3720,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3719,8 +3815,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3811,8 +3910,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3903,8 +4005,11 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3995,8 +4100,11 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4004,91 +4112,94 @@
         <v>8100</v>
       </c>
       <c r="E48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F48" s="3">
         <v>8200</v>
-      </c>
-      <c r="F48" s="3">
-        <v>8400</v>
       </c>
       <c r="G48" s="3">
         <v>8400</v>
       </c>
       <c r="H48" s="3">
+        <v>8400</v>
+      </c>
+      <c r="I48" s="3">
         <v>8500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>9100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5500</v>
-      </c>
-      <c r="V48" s="3">
-        <v>5700</v>
       </c>
       <c r="W48" s="3">
         <v>5700</v>
       </c>
       <c r="X48" s="3">
+        <v>5700</v>
+      </c>
+      <c r="Y48" s="3">
         <v>5800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6000</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>6100</v>
       </c>
       <c r="AA48" s="3">
         <v>6100</v>
       </c>
       <c r="AB48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AC48" s="3">
         <v>5600</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>5700</v>
       </c>
       <c r="AD48" s="3">
         <v>5700</v>
       </c>
       <c r="AE48" s="3">
+        <v>5700</v>
+      </c>
+      <c r="AF48" s="3">
         <v>5600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4179,8 +4290,11 @@
       <c r="AF49" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4271,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4363,8 +4480,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4446,17 +4566,20 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
+      <c r="AD52" s="3">
+        <v>0</v>
       </c>
       <c r="AE52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG52" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4547,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>541500</v>
+      </c>
+      <c r="E54" s="3">
         <v>543200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>542900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>538300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>527600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>534900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>532300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>521600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>500000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>486400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>480800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>467700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>466200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>461700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>423600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>417100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>419000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>414500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>395600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>398200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>387800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>379800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>372100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>372700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>372300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>366900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>355200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>351800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>342500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>339900</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4673,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4707,8 +4837,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4799,8 +4930,11 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4891,100 +5025,106 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3800</v>
+        <v>4300</v>
       </c>
       <c r="E59" s="3">
         <v>3800</v>
       </c>
       <c r="F59" s="3">
-        <v>3400</v>
+        <v>3800</v>
       </c>
       <c r="G59" s="3">
         <v>3400</v>
       </c>
       <c r="H59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I59" s="3">
         <v>3800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>3900</v>
       </c>
       <c r="L59" s="3">
         <v>3900</v>
       </c>
       <c r="M59" s="3">
+        <v>3900</v>
+      </c>
+      <c r="N59" s="3">
         <v>4300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3100</v>
-      </c>
-      <c r="W59" s="3">
-        <v>2900</v>
       </c>
       <c r="X59" s="3">
         <v>2900</v>
       </c>
       <c r="Y59" s="3">
+        <v>2900</v>
+      </c>
+      <c r="Z59" s="3">
         <v>3300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2700</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>2000</v>
       </c>
       <c r="AE59" s="3">
         <v>2000</v>
       </c>
       <c r="AF59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AG59" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5075,8 +5215,11 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5167,8 +5310,11 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5259,8 +5405,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5351,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5443,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5535,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>497700</v>
+      </c>
+      <c r="E66" s="3">
         <v>496900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>494800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>492700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>484100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>488300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>482200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>467300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>446300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>433500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>428700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>415400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>415700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>412500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>378300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>370800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>373400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>369800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>352700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>356800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>348100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>339800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>332500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>333100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>333400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>329200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>318900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>314300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>304500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>308700</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5661,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5753,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5845,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5929,16 +6097,19 @@
         <v>0</v>
       </c>
       <c r="AD70" s="3">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="AE70" s="3">
         <v>2300</v>
       </c>
       <c r="AF70" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AG70" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6029,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E72" s="3">
         <v>59400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>59800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>58900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>57700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>56400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>55200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>54100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>53000</v>
-      </c>
-      <c r="L72" s="3">
-        <v>51900</v>
       </c>
       <c r="M72" s="3">
         <v>51900</v>
       </c>
       <c r="N72" s="3">
+        <v>51900</v>
+      </c>
+      <c r="O72" s="3">
         <v>50600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>49100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>47700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>46500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>45700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>44700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>43700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>42900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>42100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>41200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>40300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>40000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>39300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>38400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>37200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>36400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>35700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>34900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6213,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6305,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6397,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E76" s="3">
         <v>46400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>48100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>45600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>43400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>46600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>50100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>54300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>53800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>53000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>52200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>52300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>50500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>49200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>45300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>46300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>45600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>44700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>42800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>41400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>39800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>40000</v>
-      </c>
-      <c r="Y76" s="3">
-        <v>39600</v>
       </c>
       <c r="Z76" s="3">
         <v>39600</v>
       </c>
       <c r="AA76" s="3">
+        <v>39600</v>
+      </c>
+      <c r="AB76" s="3">
         <v>38900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>37800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>36300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>35300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>35800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6581,161 +6770,167 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42916</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42825</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42643</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>41547</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1500</v>
-      </c>
-      <c r="I81" s="3">
-        <v>1400</v>
       </c>
       <c r="J81" s="3">
         <v>1400</v>
       </c>
       <c r="K81" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L81" s="3">
         <v>1500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1000</v>
-      </c>
-      <c r="U81" s="3">
-        <v>1100</v>
       </c>
       <c r="V81" s="3">
         <v>1100</v>
@@ -6753,25 +6948,28 @@
         <v>1100</v>
       </c>
       <c r="AA81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB81" s="3">
         <v>1400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>900</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>1000</v>
       </c>
       <c r="AE81" s="3">
         <v>1000</v>
       </c>
       <c r="AF81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6804,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6896,8 +7095,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6988,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7080,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7172,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7264,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7356,8 +7570,11 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7448,8 +7665,11 @@
       <c r="AF89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7482,8 +7702,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7574,8 +7795,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7666,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7758,8 +7985,11 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7850,8 +8080,11 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7884,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7976,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8068,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8160,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8252,8 +8495,11 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8344,8 +8590,11 @@
       <c r="AF100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8436,8 +8685,11 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8526,6 +8778,9 @@
         <v>0</v>
       </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FFWC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FFWC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
   <si>
     <t>FFWC</t>
   </si>
@@ -656,181 +656,184 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>41547</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E8" s="3">
         <v>6000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4500</v>
-      </c>
-      <c r="J8" s="3">
-        <v>4100</v>
       </c>
       <c r="K8" s="3">
         <v>4100</v>
       </c>
       <c r="L8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="M8" s="3">
         <v>4200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4100</v>
-      </c>
-      <c r="O8" s="3">
-        <v>4300</v>
       </c>
       <c r="P8" s="3">
         <v>4300</v>
@@ -839,43 +842,43 @@
         <v>4300</v>
       </c>
       <c r="R8" s="3">
+        <v>4300</v>
+      </c>
+      <c r="S8" s="3">
         <v>4500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4100</v>
-      </c>
-      <c r="X8" s="3">
-        <v>4000</v>
       </c>
       <c r="Y8" s="3">
         <v>4000</v>
       </c>
       <c r="Z8" s="3">
-        <v>3700</v>
+        <v>4000</v>
       </c>
       <c r="AA8" s="3">
         <v>3700</v>
       </c>
       <c r="AB8" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AC8" s="3">
         <v>3800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3500</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>3300</v>
       </c>
       <c r="AE8" s="3">
         <v>3300</v>
@@ -886,8 +889,11 @@
       <c r="AG8" s="3">
         <v>3300</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -981,8 +987,11 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1076,8 +1085,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1123,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1206,8 +1219,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,8 +1317,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1396,8 +1415,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,8 +1513,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,31 +1548,32 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E17" s="3">
         <v>2400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>600</v>
-      </c>
-      <c r="J17" s="3">
-        <v>400</v>
       </c>
       <c r="K17" s="3">
         <v>400</v>
@@ -1556,55 +1582,55 @@
         <v>400</v>
       </c>
       <c r="M17" s="3">
+        <v>400</v>
+      </c>
+      <c r="N17" s="3">
         <v>200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>700</v>
-      </c>
-      <c r="P17" s="3">
-        <v>800</v>
       </c>
       <c r="Q17" s="3">
         <v>800</v>
       </c>
       <c r="R17" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="S17" s="3">
         <v>1000</v>
       </c>
       <c r="T17" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="U17" s="3">
         <v>1100</v>
       </c>
       <c r="V17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W17" s="3">
         <v>1000</v>
-      </c>
-      <c r="W17" s="3">
-        <v>800</v>
       </c>
       <c r="X17" s="3">
         <v>800</v>
       </c>
       <c r="Y17" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z17" s="3">
         <v>500</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>600</v>
       </c>
       <c r="AA17" s="3">
         <v>600</v>
       </c>
       <c r="AB17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC17" s="3">
         <v>100</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>500</v>
       </c>
       <c r="AD17" s="3">
         <v>500</v>
@@ -1613,54 +1639,57 @@
         <v>500</v>
       </c>
       <c r="AF17" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG17" s="3">
         <v>600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E18" s="3">
         <v>3600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3900</v>
-      </c>
-      <c r="J18" s="3">
-        <v>3700</v>
       </c>
       <c r="K18" s="3">
         <v>3700</v>
       </c>
       <c r="L18" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="M18" s="3">
         <v>3800</v>
       </c>
       <c r="N18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="O18" s="3">
         <v>3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3600</v>
-      </c>
-      <c r="P18" s="3">
-        <v>3500</v>
       </c>
       <c r="Q18" s="3">
         <v>3500</v>
@@ -1669,52 +1698,55 @@
         <v>3500</v>
       </c>
       <c r="S18" s="3">
+        <v>3500</v>
+      </c>
+      <c r="T18" s="3">
         <v>3300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3400</v>
-      </c>
-      <c r="U18" s="3">
-        <v>3200</v>
       </c>
       <c r="V18" s="3">
         <v>3200</v>
       </c>
       <c r="W18" s="3">
+        <v>3200</v>
+      </c>
+      <c r="X18" s="3">
         <v>3300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3500</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>3100</v>
       </c>
       <c r="AA18" s="3">
         <v>3100</v>
       </c>
       <c r="AB18" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AC18" s="3">
         <v>3700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3000</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>2800</v>
       </c>
       <c r="AE18" s="3">
         <v>2800</v>
       </c>
       <c r="AF18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AG18" s="3">
         <v>2700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,28 +1780,29 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-2200</v>
       </c>
       <c r="J20" s="3">
         <v>-2200</v>
@@ -1778,31 +1811,31 @@
         <v>-2200</v>
       </c>
       <c r="L20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="M20" s="3">
         <v>-2000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-1400</v>
       </c>
       <c r="P20" s="3">
         <v>-1400</v>
       </c>
       <c r="Q20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-2000</v>
       </c>
       <c r="U20" s="3">
         <v>-2000</v>
@@ -1814,13 +1847,13 @@
         <v>-2000</v>
       </c>
       <c r="X20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2100</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-1800</v>
       </c>
       <c r="AA20" s="3">
         <v>-1800</v>
@@ -1829,22 +1862,25 @@
         <v>-1800</v>
       </c>
       <c r="AC20" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="AD20" s="3">
         <v>-1700</v>
       </c>
       <c r="AE20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1938,8 +1974,11 @@
       <c r="AG21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2033,76 +2072,79 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E23" s="3">
         <v>1100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1700</v>
-      </c>
-      <c r="J23" s="3">
-        <v>1500</v>
       </c>
       <c r="K23" s="3">
         <v>1500</v>
       </c>
       <c r="L23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M23" s="3">
         <v>1800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1800</v>
-      </c>
-      <c r="O23" s="3">
-        <v>2100</v>
       </c>
       <c r="P23" s="3">
         <v>2100</v>
       </c>
       <c r="Q23" s="3">
+        <v>2100</v>
+      </c>
+      <c r="R23" s="3">
         <v>1700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1400</v>
-      </c>
-      <c r="U23" s="3">
-        <v>1200</v>
       </c>
       <c r="V23" s="3">
         <v>1200</v>
       </c>
       <c r="W23" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="X23" s="3">
         <v>1300</v>
       </c>
       <c r="Y23" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="Z23" s="3">
         <v>1400</v>
@@ -2111,25 +2153,28 @@
         <v>1400</v>
       </c>
       <c r="AB23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AC23" s="3">
         <v>1900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1100</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>1300</v>
       </c>
       <c r="AF23" s="3">
         <v>1300</v>
       </c>
       <c r="AG23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AH23" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2143,28 +2188,28 @@
         <v>100</v>
       </c>
       <c r="G24" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H24" s="3">
         <v>300</v>
       </c>
       <c r="I24" s="3">
+        <v>300</v>
+      </c>
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
-      </c>
-      <c r="N24" s="3">
-        <v>300</v>
       </c>
       <c r="O24" s="3">
         <v>300</v>
@@ -2176,7 +2221,7 @@
         <v>300</v>
       </c>
       <c r="R24" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="S24" s="3">
         <v>200</v>
@@ -2185,16 +2230,16 @@
         <v>200</v>
       </c>
       <c r="U24" s="3">
+        <v>200</v>
+      </c>
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100</v>
-      </c>
-      <c r="X24" s="3">
-        <v>200</v>
       </c>
       <c r="Y24" s="3">
         <v>200</v>
@@ -2206,25 +2251,28 @@
         <v>200</v>
       </c>
       <c r="AB24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC24" s="3">
         <v>500</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>200</v>
       </c>
       <c r="AD24" s="3">
         <v>200</v>
       </c>
       <c r="AE24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AF24" s="3">
         <v>300</v>
       </c>
       <c r="AG24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,67 +2366,70 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1500</v>
-      </c>
-      <c r="J26" s="3">
-        <v>1400</v>
       </c>
       <c r="K26" s="3">
         <v>1400</v>
       </c>
       <c r="L26" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M26" s="3">
         <v>1500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1000</v>
-      </c>
-      <c r="V26" s="3">
-        <v>1100</v>
       </c>
       <c r="W26" s="3">
         <v>1100</v>
@@ -2396,84 +2447,87 @@
         <v>1100</v>
       </c>
       <c r="AB26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC26" s="3">
         <v>1400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>900</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>1000</v>
       </c>
       <c r="AF26" s="3">
         <v>1000</v>
       </c>
       <c r="AG26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E27" s="3">
         <v>1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1500</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1400</v>
       </c>
       <c r="K27" s="3">
         <v>1400</v>
       </c>
       <c r="L27" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M27" s="3">
         <v>1500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1000</v>
-      </c>
-      <c r="V27" s="3">
-        <v>1100</v>
       </c>
       <c r="W27" s="3">
         <v>1100</v>
@@ -2491,25 +2545,28 @@
         <v>1100</v>
       </c>
       <c r="AB27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC27" s="3">
         <v>1400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>900</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>1000</v>
       </c>
       <c r="AF27" s="3">
         <v>1000</v>
       </c>
       <c r="AG27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2660,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2758,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2856,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,28 +2954,31 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E32" s="3">
         <v>2600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>2200</v>
       </c>
       <c r="J32" s="3">
         <v>2200</v>
@@ -2918,31 +2987,31 @@
         <v>2200</v>
       </c>
       <c r="L32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M32" s="3">
         <v>2000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1600</v>
-      </c>
-      <c r="O32" s="3">
-        <v>1400</v>
       </c>
       <c r="P32" s="3">
         <v>1400</v>
       </c>
       <c r="Q32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="R32" s="3">
         <v>1900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1800</v>
-      </c>
-      <c r="T32" s="3">
-        <v>2000</v>
       </c>
       <c r="U32" s="3">
         <v>2000</v>
@@ -2954,13 +3023,13 @@
         <v>2000</v>
       </c>
       <c r="X32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Y32" s="3">
         <v>1900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2100</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>1800</v>
       </c>
       <c r="AA32" s="3">
         <v>1800</v>
@@ -2969,81 +3038,84 @@
         <v>1800</v>
       </c>
       <c r="AC32" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="AD32" s="3">
         <v>1700</v>
       </c>
       <c r="AE32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AF32" s="3">
         <v>1500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E33" s="3">
         <v>1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1500</v>
-      </c>
-      <c r="J33" s="3">
-        <v>1400</v>
       </c>
       <c r="K33" s="3">
         <v>1400</v>
       </c>
       <c r="L33" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M33" s="3">
         <v>1500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1000</v>
-      </c>
-      <c r="V33" s="3">
-        <v>1100</v>
       </c>
       <c r="W33" s="3">
         <v>1100</v>
@@ -3061,25 +3133,28 @@
         <v>1100</v>
       </c>
       <c r="AB33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC33" s="3">
         <v>1400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>900</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>1000</v>
       </c>
       <c r="AF33" s="3">
         <v>1000</v>
       </c>
       <c r="AG33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,67 +3248,70 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E35" s="3">
         <v>1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1500</v>
-      </c>
-      <c r="J35" s="3">
-        <v>1400</v>
       </c>
       <c r="K35" s="3">
         <v>1400</v>
       </c>
       <c r="L35" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M35" s="3">
         <v>1500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1000</v>
-      </c>
-      <c r="V35" s="3">
-        <v>1100</v>
       </c>
       <c r="W35" s="3">
         <v>1100</v>
@@ -3251,125 +3329,131 @@
         <v>1100</v>
       </c>
       <c r="AB35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC35" s="3">
         <v>1400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>900</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>1000</v>
       </c>
       <c r="AF35" s="3">
         <v>1000</v>
       </c>
       <c r="AG35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>41547</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3487,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,198 +3523,205 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E41" s="3">
         <v>6100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E42" s="3">
         <v>4600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>14200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>49700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>63100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>66000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>49500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>53100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>43400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>23600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>28400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>31500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>14000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>16500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>13100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>23300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>21100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>24900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>17900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>13200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>9000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>16600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>19700</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>16900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>17300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>15500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>7100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3723,8 +3815,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,8 +3913,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3913,8 +4011,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4008,8 +4109,11 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4103,103 +4207,109 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>8100</v>
+        <v>7900</v>
       </c>
       <c r="E48" s="3">
         <v>8100</v>
       </c>
       <c r="F48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="G48" s="3">
         <v>8200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>8400</v>
       </c>
       <c r="H48" s="3">
         <v>8400</v>
       </c>
       <c r="I48" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J48" s="3">
         <v>8500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>9100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5500</v>
-      </c>
-      <c r="W48" s="3">
-        <v>5700</v>
       </c>
       <c r="X48" s="3">
         <v>5700</v>
       </c>
       <c r="Y48" s="3">
+        <v>5700</v>
+      </c>
+      <c r="Z48" s="3">
         <v>5800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6000</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>6100</v>
       </c>
       <c r="AB48" s="3">
         <v>6100</v>
       </c>
       <c r="AC48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AD48" s="3">
         <v>5600</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>5700</v>
       </c>
       <c r="AE48" s="3">
         <v>5700</v>
       </c>
       <c r="AF48" s="3">
+        <v>5700</v>
+      </c>
+      <c r="AG48" s="3">
         <v>5600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4293,8 +4403,11 @@
       <c r="AG49" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4501,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,8 +4599,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4569,17 +4688,20 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-      <c r="AE52" s="3" t="s">
-        <v>5</v>
+      <c r="AE52" s="3">
+        <v>0</v>
       </c>
       <c r="AF52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH52" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4795,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>554200</v>
+      </c>
+      <c r="E54" s="3">
         <v>541500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>543200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>542900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>538300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>527600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>534900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>532300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>521600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>500000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>486400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>480800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>467700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>466200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>461700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>423600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>417100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>419000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>414500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>395600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>398200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>387800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>379800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>372100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>372700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>372300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>366900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>355200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>351800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>342500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>339900</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4931,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,8 +4967,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4933,8 +5063,11 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5028,103 +5161,109 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E59" s="3">
         <v>4300</v>
-      </c>
-      <c r="E59" s="3">
-        <v>3800</v>
       </c>
       <c r="F59" s="3">
         <v>3800</v>
       </c>
       <c r="G59" s="3">
-        <v>3400</v>
+        <v>3800</v>
       </c>
       <c r="H59" s="3">
         <v>3400</v>
       </c>
       <c r="I59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J59" s="3">
         <v>3800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>3900</v>
       </c>
       <c r="M59" s="3">
         <v>3900</v>
       </c>
       <c r="N59" s="3">
+        <v>3900</v>
+      </c>
+      <c r="O59" s="3">
         <v>4300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3100</v>
-      </c>
-      <c r="X59" s="3">
-        <v>2900</v>
       </c>
       <c r="Y59" s="3">
         <v>2900</v>
       </c>
       <c r="Z59" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AA59" s="3">
         <v>3300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2700</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>2000</v>
       </c>
       <c r="AF59" s="3">
         <v>2000</v>
       </c>
       <c r="AG59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AH59" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5218,8 +5357,11 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5313,8 +5455,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5408,8 +5553,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5651,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5749,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5847,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>505700</v>
+      </c>
+      <c r="E66" s="3">
         <v>497700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>496900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>494800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>492700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>484100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>488300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>482200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>467300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>446300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>433500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>428700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>415400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>415700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>412500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>378300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>370800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>373400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>369800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>352700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>356800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>348100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>339800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>332500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>333100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>333400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>329200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>318900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>314300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>304500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>308700</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5983,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6079,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6177,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6100,16 +6267,19 @@
         <v>0</v>
       </c>
       <c r="AE70" s="3">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="AF70" s="3">
         <v>2300</v>
       </c>
       <c r="AG70" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AH70" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6373,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>60300</v>
+      </c>
+      <c r="E72" s="3">
         <v>59600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>59400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>59800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>58900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>57700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>56400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>55200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>54100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>53000</v>
-      </c>
-      <c r="M72" s="3">
-        <v>51900</v>
       </c>
       <c r="N72" s="3">
         <v>51900</v>
       </c>
       <c r="O72" s="3">
+        <v>51900</v>
+      </c>
+      <c r="P72" s="3">
         <v>50600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>49100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>47700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>46500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>45700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>44700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>43700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>42900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>42100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>41200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>40300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>40000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>39300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>38400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>37200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>36400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>35700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>34900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6569,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6667,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6765,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E76" s="3">
         <v>43800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>46400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>48100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>45600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>43400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>46600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>50100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>54300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>53800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>53000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>52200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>52300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>50500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>49200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>45300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>46300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>45600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>44700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>42800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>41400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>39800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>40000</v>
-      </c>
-      <c r="Z76" s="3">
-        <v>39600</v>
       </c>
       <c r="AA76" s="3">
         <v>39600</v>
       </c>
       <c r="AB76" s="3">
+        <v>39600</v>
+      </c>
+      <c r="AC76" s="3">
         <v>38900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>37800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>36300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>35300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>35800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,167 +6961,173 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>41547</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E81" s="3">
         <v>1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1500</v>
-      </c>
-      <c r="J81" s="3">
-        <v>1400</v>
       </c>
       <c r="K81" s="3">
         <v>1400</v>
       </c>
       <c r="L81" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M81" s="3">
         <v>1500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1000</v>
-      </c>
-      <c r="V81" s="3">
-        <v>1100</v>
       </c>
       <c r="W81" s="3">
         <v>1100</v>
@@ -6951,25 +7145,28 @@
         <v>1100</v>
       </c>
       <c r="AB81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AC81" s="3">
         <v>1400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>900</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>1000</v>
       </c>
       <c r="AF81" s="3">
         <v>1000</v>
       </c>
       <c r="AG81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7200,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7098,8 +7296,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7394,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7492,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7590,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7688,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,8 +7786,11 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7668,8 +7884,11 @@
       <c r="AG89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,8 +7922,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7798,8 +8018,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8116,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,8 +8214,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8083,8 +8312,11 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8350,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8446,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8544,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8642,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,8 +8740,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8593,8 +8838,11 @@
       <c r="AG100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8688,8 +8936,11 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8781,6 +9032,9 @@
         <v>0</v>
       </c>
       <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FFWC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FFWC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
   <si>
     <t>FFWC</t>
   </si>
@@ -656,146 +656,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>41547</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -803,40 +807,40 @@
         <v>6300</v>
       </c>
       <c r="E8" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F8" s="3">
         <v>6000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4500</v>
-      </c>
-      <c r="K8" s="3">
-        <v>4100</v>
       </c>
       <c r="L8" s="3">
         <v>4100</v>
       </c>
       <c r="M8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="N8" s="3">
         <v>4200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4100</v>
-      </c>
-      <c r="P8" s="3">
-        <v>4300</v>
       </c>
       <c r="Q8" s="3">
         <v>4300</v>
@@ -845,43 +849,43 @@
         <v>4300</v>
       </c>
       <c r="S8" s="3">
+        <v>4300</v>
+      </c>
+      <c r="T8" s="3">
         <v>4500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4100</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>4000</v>
       </c>
       <c r="Z8" s="3">
         <v>4000</v>
       </c>
       <c r="AA8" s="3">
-        <v>3700</v>
+        <v>4000</v>
       </c>
       <c r="AB8" s="3">
         <v>3700</v>
       </c>
       <c r="AC8" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AD8" s="3">
         <v>3800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3500</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>3300</v>
       </c>
       <c r="AF8" s="3">
         <v>3300</v>
@@ -892,8 +896,11 @@
       <c r="AH8" s="3">
         <v>3300</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -990,8 +997,11 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1088,8 +1098,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1124,8 +1137,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1222,8 +1236,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1320,8 +1337,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1418,8 +1438,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1516,8 +1539,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1549,34 +1575,35 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E17" s="3">
         <v>2600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>600</v>
-      </c>
-      <c r="K17" s="3">
-        <v>400</v>
       </c>
       <c r="L17" s="3">
         <v>400</v>
@@ -1585,55 +1612,55 @@
         <v>400</v>
       </c>
       <c r="N17" s="3">
+        <v>400</v>
+      </c>
+      <c r="O17" s="3">
         <v>200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>700</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>800</v>
       </c>
       <c r="R17" s="3">
         <v>800</v>
       </c>
       <c r="S17" s="3">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="T17" s="3">
         <v>1000</v>
       </c>
       <c r="U17" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="V17" s="3">
         <v>1100</v>
       </c>
       <c r="W17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X17" s="3">
         <v>1000</v>
-      </c>
-      <c r="X17" s="3">
-        <v>800</v>
       </c>
       <c r="Y17" s="3">
         <v>800</v>
       </c>
       <c r="Z17" s="3">
+        <v>800</v>
+      </c>
+      <c r="AA17" s="3">
         <v>500</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>600</v>
       </c>
       <c r="AB17" s="3">
         <v>600</v>
       </c>
       <c r="AC17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD17" s="3">
         <v>100</v>
-      </c>
-      <c r="AD17" s="3">
-        <v>500</v>
       </c>
       <c r="AE17" s="3">
         <v>500</v>
@@ -1642,57 +1669,60 @@
         <v>500</v>
       </c>
       <c r="AG17" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH17" s="3">
         <v>600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E18" s="3">
         <v>3700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3900</v>
-      </c>
-      <c r="K18" s="3">
-        <v>3700</v>
       </c>
       <c r="L18" s="3">
         <v>3700</v>
       </c>
       <c r="M18" s="3">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="N18" s="3">
         <v>3800</v>
       </c>
       <c r="O18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="P18" s="3">
         <v>3500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3600</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>3500</v>
       </c>
       <c r="R18" s="3">
         <v>3500</v>
@@ -1701,52 +1731,55 @@
         <v>3500</v>
       </c>
       <c r="T18" s="3">
+        <v>3500</v>
+      </c>
+      <c r="U18" s="3">
         <v>3300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3400</v>
-      </c>
-      <c r="V18" s="3">
-        <v>3200</v>
       </c>
       <c r="W18" s="3">
         <v>3200</v>
       </c>
       <c r="X18" s="3">
+        <v>3200</v>
+      </c>
+      <c r="Y18" s="3">
         <v>3300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3500</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>3100</v>
       </c>
       <c r="AB18" s="3">
         <v>3100</v>
       </c>
       <c r="AC18" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AD18" s="3">
         <v>3700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3000</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>2800</v>
       </c>
       <c r="AF18" s="3">
         <v>2800</v>
       </c>
       <c r="AG18" s="3">
+        <v>2800</v>
+      </c>
+      <c r="AH18" s="3">
         <v>2700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2400</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1781,8 +1814,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1790,22 +1824,22 @@
         <v>-2500</v>
       </c>
       <c r="E20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F20" s="3">
         <v>-2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-2200</v>
       </c>
       <c r="K20" s="3">
         <v>-2200</v>
@@ -1814,31 +1848,31 @@
         <v>-2200</v>
       </c>
       <c r="M20" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="N20" s="3">
         <v>-2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1600</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-1400</v>
       </c>
       <c r="Q20" s="3">
         <v>-1400</v>
       </c>
       <c r="R20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1800</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-2000</v>
       </c>
       <c r="V20" s="3">
         <v>-2000</v>
@@ -1850,13 +1884,13 @@
         <v>-2000</v>
       </c>
       <c r="Y20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2100</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-1800</v>
       </c>
       <c r="AB20" s="3">
         <v>-1800</v>
@@ -1865,22 +1899,25 @@
         <v>-1800</v>
       </c>
       <c r="AD20" s="3">
-        <v>-1700</v>
+        <v>-1800</v>
       </c>
       <c r="AE20" s="3">
         <v>-1700</v>
       </c>
       <c r="AF20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1600</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1977,8 +2014,11 @@
       <c r="AH21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2075,79 +2115,82 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1700</v>
-      </c>
-      <c r="K23" s="3">
-        <v>1500</v>
       </c>
       <c r="L23" s="3">
         <v>1500</v>
       </c>
       <c r="M23" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N23" s="3">
         <v>1800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1800</v>
-      </c>
-      <c r="P23" s="3">
-        <v>2100</v>
       </c>
       <c r="Q23" s="3">
         <v>2100</v>
       </c>
       <c r="R23" s="3">
+        <v>2100</v>
+      </c>
+      <c r="S23" s="3">
         <v>1700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1400</v>
-      </c>
-      <c r="V23" s="3">
-        <v>1200</v>
       </c>
       <c r="W23" s="3">
         <v>1200</v>
       </c>
       <c r="X23" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="Y23" s="3">
         <v>1300</v>
       </c>
       <c r="Z23" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="AA23" s="3">
         <v>1400</v>
@@ -2156,25 +2199,28 @@
         <v>1400</v>
       </c>
       <c r="AC23" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AD23" s="3">
         <v>1900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1100</v>
-      </c>
-      <c r="AF23" s="3">
-        <v>1300</v>
       </c>
       <c r="AG23" s="3">
         <v>1300</v>
       </c>
       <c r="AH23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AI23" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2191,28 +2237,28 @@
         <v>100</v>
       </c>
       <c r="H24" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I24" s="3">
         <v>300</v>
       </c>
       <c r="J24" s="3">
+        <v>300</v>
+      </c>
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
-      </c>
-      <c r="O24" s="3">
-        <v>300</v>
       </c>
       <c r="P24" s="3">
         <v>300</v>
@@ -2224,7 +2270,7 @@
         <v>300</v>
       </c>
       <c r="S24" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T24" s="3">
         <v>200</v>
@@ -2233,16 +2279,16 @@
         <v>200</v>
       </c>
       <c r="V24" s="3">
+        <v>200</v>
+      </c>
+      <c r="W24" s="3">
         <v>100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>100</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>200</v>
       </c>
       <c r="Z24" s="3">
         <v>200</v>
@@ -2254,25 +2300,28 @@
         <v>200</v>
       </c>
       <c r="AC24" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD24" s="3">
         <v>500</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>200</v>
       </c>
       <c r="AE24" s="3">
         <v>200</v>
       </c>
       <c r="AF24" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AG24" s="3">
         <v>300</v>
       </c>
       <c r="AH24" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2369,70 +2418,73 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>900</v>
+      </c>
+      <c r="E26" s="3">
         <v>1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1500</v>
-      </c>
-      <c r="K26" s="3">
-        <v>1400</v>
       </c>
       <c r="L26" s="3">
         <v>1400</v>
       </c>
       <c r="M26" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N26" s="3">
         <v>1500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1000</v>
-      </c>
-      <c r="W26" s="3">
-        <v>1100</v>
       </c>
       <c r="X26" s="3">
         <v>1100</v>
@@ -2450,87 +2502,90 @@
         <v>1100</v>
       </c>
       <c r="AC26" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD26" s="3">
         <v>1400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>900</v>
-      </c>
-      <c r="AF26" s="3">
-        <v>1000</v>
       </c>
       <c r="AG26" s="3">
         <v>1000</v>
       </c>
       <c r="AH26" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AI26" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>900</v>
+      </c>
+      <c r="E27" s="3">
         <v>1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1500</v>
-      </c>
-      <c r="K27" s="3">
-        <v>1400</v>
       </c>
       <c r="L27" s="3">
         <v>1400</v>
       </c>
       <c r="M27" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N27" s="3">
         <v>1500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1000</v>
-      </c>
-      <c r="W27" s="3">
-        <v>1100</v>
       </c>
       <c r="X27" s="3">
         <v>1100</v>
@@ -2548,25 +2603,28 @@
         <v>1100</v>
       </c>
       <c r="AC27" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD27" s="3">
         <v>1400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>900</v>
-      </c>
-      <c r="AF27" s="3">
-        <v>1000</v>
       </c>
       <c r="AG27" s="3">
         <v>1000</v>
       </c>
       <c r="AH27" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AI27" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2663,8 +2721,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2761,8 +2822,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2859,8 +2923,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2957,8 +3024,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2966,22 +3036,22 @@
         <v>2500</v>
       </c>
       <c r="E32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F32" s="3">
         <v>2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>2200</v>
       </c>
       <c r="K32" s="3">
         <v>2200</v>
@@ -2990,31 +3060,31 @@
         <v>2200</v>
       </c>
       <c r="M32" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N32" s="3">
         <v>2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1600</v>
-      </c>
-      <c r="P32" s="3">
-        <v>1400</v>
       </c>
       <c r="Q32" s="3">
         <v>1400</v>
       </c>
       <c r="R32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="S32" s="3">
         <v>1900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1800</v>
-      </c>
-      <c r="U32" s="3">
-        <v>2000</v>
       </c>
       <c r="V32" s="3">
         <v>2000</v>
@@ -3026,13 +3096,13 @@
         <v>2000</v>
       </c>
       <c r="Y32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2100</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>1800</v>
       </c>
       <c r="AB32" s="3">
         <v>1800</v>
@@ -3041,84 +3111,87 @@
         <v>1800</v>
       </c>
       <c r="AD32" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="AE32" s="3">
         <v>1700</v>
       </c>
       <c r="AF32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AG32" s="3">
         <v>1500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>900</v>
+      </c>
+      <c r="E33" s="3">
         <v>1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1500</v>
-      </c>
-      <c r="K33" s="3">
-        <v>1400</v>
       </c>
       <c r="L33" s="3">
         <v>1400</v>
       </c>
       <c r="M33" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N33" s="3">
         <v>1500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1000</v>
-      </c>
-      <c r="W33" s="3">
-        <v>1100</v>
       </c>
       <c r="X33" s="3">
         <v>1100</v>
@@ -3136,25 +3209,28 @@
         <v>1100</v>
       </c>
       <c r="AC33" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD33" s="3">
         <v>1400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>900</v>
-      </c>
-      <c r="AF33" s="3">
-        <v>1000</v>
       </c>
       <c r="AG33" s="3">
         <v>1000</v>
       </c>
       <c r="AH33" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AI33" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3251,70 +3327,73 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>900</v>
+      </c>
+      <c r="E35" s="3">
         <v>1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1500</v>
-      </c>
-      <c r="K35" s="3">
-        <v>1400</v>
       </c>
       <c r="L35" s="3">
         <v>1400</v>
       </c>
       <c r="M35" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N35" s="3">
         <v>1500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1000</v>
-      </c>
-      <c r="W35" s="3">
-        <v>1100</v>
       </c>
       <c r="X35" s="3">
         <v>1100</v>
@@ -3332,128 +3411,134 @@
         <v>1100</v>
       </c>
       <c r="AC35" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD35" s="3">
         <v>1400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>900</v>
-      </c>
-      <c r="AF35" s="3">
-        <v>1000</v>
       </c>
       <c r="AG35" s="3">
         <v>1000</v>
       </c>
       <c r="AH35" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AI35" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>41547</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3488,8 +3573,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3524,204 +3610,211 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E41" s="3">
         <v>5800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>6300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E42" s="3">
         <v>4000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>14200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>12100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>49700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>63100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>66000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>49500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>53100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>43400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>23600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>28400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>31500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>14000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>16500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>13100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>23300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>21100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>24900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>17900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>13200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>9000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>16600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>19700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>16900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>17300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>15500</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>7100</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>8800</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3818,8 +3911,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3916,8 +4012,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4014,8 +4113,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4112,8 +4214,11 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4210,106 +4315,112 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E48" s="3">
         <v>7900</v>
-      </c>
-      <c r="E48" s="3">
-        <v>8100</v>
       </c>
       <c r="F48" s="3">
         <v>8100</v>
       </c>
       <c r="G48" s="3">
+        <v>8100</v>
+      </c>
+      <c r="H48" s="3">
         <v>8200</v>
-      </c>
-      <c r="H48" s="3">
-        <v>8400</v>
       </c>
       <c r="I48" s="3">
         <v>8400</v>
       </c>
       <c r="J48" s="3">
+        <v>8400</v>
+      </c>
+      <c r="K48" s="3">
         <v>8500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>9100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>9300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>9400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>9300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5500</v>
-      </c>
-      <c r="X48" s="3">
-        <v>5700</v>
       </c>
       <c r="Y48" s="3">
         <v>5700</v>
       </c>
       <c r="Z48" s="3">
+        <v>5700</v>
+      </c>
+      <c r="AA48" s="3">
         <v>5800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6000</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>6100</v>
       </c>
       <c r="AC48" s="3">
         <v>6100</v>
       </c>
       <c r="AD48" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AE48" s="3">
         <v>5600</v>
-      </c>
-      <c r="AE48" s="3">
-        <v>5700</v>
       </c>
       <c r="AF48" s="3">
         <v>5700</v>
       </c>
       <c r="AG48" s="3">
+        <v>5700</v>
+      </c>
+      <c r="AH48" s="3">
         <v>5600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4406,8 +4517,11 @@
       <c r="AH49" s="3">
         <v>1200</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4504,8 +4618,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4602,8 +4719,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4691,17 +4811,20 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
+      <c r="AF52" s="3">
+        <v>0</v>
       </c>
       <c r="AG52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AH52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI52" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4798,106 +4921,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>556700</v>
+      </c>
+      <c r="E54" s="3">
         <v>554200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>541500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>543200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>542900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>538300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>527600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>534900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>532300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>521600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>500000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>486400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>480800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>467700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>466200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>461700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>423600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>417100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>419000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>414500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>395600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>398200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>387800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>379800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>372100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>372700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>372300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>366900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>355200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>351800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>342500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>339900</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4932,8 +5061,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4968,8 +5098,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5066,8 +5197,11 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5164,106 +5298,112 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E59" s="3">
         <v>4600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>3800</v>
       </c>
       <c r="G59" s="3">
         <v>3800</v>
       </c>
       <c r="H59" s="3">
-        <v>3400</v>
+        <v>3800</v>
       </c>
       <c r="I59" s="3">
         <v>3400</v>
       </c>
       <c r="J59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K59" s="3">
         <v>3800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4000</v>
-      </c>
-      <c r="M59" s="3">
-        <v>3900</v>
       </c>
       <c r="N59" s="3">
         <v>3900</v>
       </c>
       <c r="O59" s="3">
+        <v>3900</v>
+      </c>
+      <c r="P59" s="3">
         <v>4300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3100</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>2900</v>
       </c>
       <c r="Z59" s="3">
         <v>2900</v>
       </c>
       <c r="AA59" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AB59" s="3">
         <v>3300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2700</v>
-      </c>
-      <c r="AF59" s="3">
-        <v>2000</v>
       </c>
       <c r="AG59" s="3">
         <v>2000</v>
       </c>
       <c r="AH59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AI59" s="3">
         <v>1800</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5360,8 +5500,11 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5458,8 +5601,11 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5556,8 +5702,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5654,8 +5803,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5752,8 +5904,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5850,106 +6005,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>508700</v>
+      </c>
+      <c r="E66" s="3">
         <v>505700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>497700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>496900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>494800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>492700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>484100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>488300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>482200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>467300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>446300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>433500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>428700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>415400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>415700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>412500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>378300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>370800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>373400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>369800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>352700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>356800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>348100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>339800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>332500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>333100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>333400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>329200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>318900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>314300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>304500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>308700</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5984,8 +6145,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6082,8 +6244,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6180,8 +6345,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6270,16 +6438,19 @@
         <v>0</v>
       </c>
       <c r="AF70" s="3">
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="AG70" s="3">
         <v>2300</v>
       </c>
       <c r="AH70" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AI70" s="3">
         <v>7600</v>
       </c>
     </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6376,106 +6547,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E72" s="3">
         <v>60300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>59600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>59400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>59800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>58900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>57700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>56400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>55200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>54100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>53000</v>
-      </c>
-      <c r="N72" s="3">
-        <v>51900</v>
       </c>
       <c r="O72" s="3">
         <v>51900</v>
       </c>
       <c r="P72" s="3">
+        <v>51900</v>
+      </c>
+      <c r="Q72" s="3">
         <v>50600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>49100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>47700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>46500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>45700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>44700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>43700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>42900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>42100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>41200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>40300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>40000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>39300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>38400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>37200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>36400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>35700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>34900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>26100</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6572,8 +6749,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6670,8 +6850,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6768,106 +6951,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E76" s="3">
         <v>48500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>43800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>46400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>48100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>45600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>43400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>46600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>50100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>54300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>53800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>53000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>52200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>52300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>50500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>49200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>45300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>46300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>45600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>44700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>42800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>41400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>39800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>40000</v>
-      </c>
-      <c r="AA76" s="3">
-        <v>39600</v>
       </c>
       <c r="AB76" s="3">
         <v>39600</v>
       </c>
       <c r="AC76" s="3">
+        <v>39600</v>
+      </c>
+      <c r="AD76" s="3">
         <v>38900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>37800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>36300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>35300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>35800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>23500</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6964,173 +7153,179 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>41547</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>900</v>
+      </c>
+      <c r="E81" s="3">
         <v>1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1500</v>
-      </c>
-      <c r="K81" s="3">
-        <v>1400</v>
       </c>
       <c r="L81" s="3">
         <v>1400</v>
       </c>
       <c r="M81" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N81" s="3">
         <v>1500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1000</v>
-      </c>
-      <c r="W81" s="3">
-        <v>1100</v>
       </c>
       <c r="X81" s="3">
         <v>1100</v>
@@ -7148,25 +7343,28 @@
         <v>1100</v>
       </c>
       <c r="AC81" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD81" s="3">
         <v>1400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>900</v>
-      </c>
-      <c r="AF81" s="3">
-        <v>1000</v>
       </c>
       <c r="AG81" s="3">
         <v>1000</v>
       </c>
       <c r="AH81" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AI81" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7201,8 +7399,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7299,8 +7498,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7397,8 +7599,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7495,8 +7700,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7593,8 +7801,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7691,8 +7902,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7789,8 +8003,11 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7887,8 +8104,11 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7923,8 +8143,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8021,8 +8242,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8119,8 +8343,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8217,8 +8444,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8315,8 +8545,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8351,8 +8584,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8449,8 +8683,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8547,8 +8784,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8645,8 +8885,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8743,8 +8986,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8841,8 +9087,11 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8939,8 +9188,11 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9035,6 +9287,9 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
